--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,35 +444,40 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>problem_type</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>problem</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>score_text</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>runtime_text</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>submitted_at</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>paid</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>members</t>
         </is>
@@ -486,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Alpha Coders </t>
+          <t xml:space="preserve">Alpha Coders </t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -496,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MACAU</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -506,35 +511,40 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>A - Data Cleanup</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Score: 88/100</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>1m 42s</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>2026-04-21 19:05</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Alice; Bob; Charlie</t>
         </is>
@@ -548,17 +558,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>byte force</t>
+          <t>Byte Force</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pui Ching middle school</t>
+          <t>Pui Ching Middle School</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MACAU</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -568,35 +578,40 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>B: Text Parser</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>76 pts</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>98 sec</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Python3</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026/04/21 19:12</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Ben, Cathy</t>
         </is>
@@ -620,7 +635,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TAIPA</t>
+          <t>Taipa</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -630,35 +645,40 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>A - Data Cleanup</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>2 min 05 sec</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>py</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>21-04-2026 19:18</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>David; Eva</t>
         </is>
@@ -682,41 +702,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TAIPA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>Taipa</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>UNKNOW</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>C - Group Stats</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>00:01:31</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>PYTHON</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>2026-04-21 19:30</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Fiona; Gary; Helen</t>
         </is>
@@ -730,7 +759,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> pandas pandas </t>
+          <t xml:space="preserve">Pandas Pandas </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -740,7 +769,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MACAU</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -750,31 +779,36 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>A - Data Cleanup</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>84/100</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>1:55</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>2026-04-21 19:36</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Iris</t>
         </is>
@@ -798,7 +832,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MACAU ISLAND</t>
+          <t>Macau Island</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -808,35 +842,40 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>B: Text Parser</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Score = 69</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>145 seconds</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>2026-04-21 19:42</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Jack; Kelly</t>
         </is>
@@ -860,7 +899,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MACAU</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -870,35 +909,40 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>B: Text Parser</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>95 points</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>1m05s</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>2026-04-21 19:50</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Leo; Mike</t>
         </is>
@@ -912,7 +956,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CSV Avengers</t>
+          <t>Csv Avengers</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -922,7 +966,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MACAU</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -932,27 +976,32 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>C - Group Stats</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>2026-04-21 19:55</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Nora; Oscar</t>
         </is>
@@ -976,7 +1025,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>TAIPA</t>
+          <t>Taipa</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -986,35 +1035,40 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>A - Data Cleanup</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>78 percent</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>2m 20s</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>PY</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>2026-04-21 20:02</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Paul; Queenie</t>
         </is>
@@ -1038,7 +1092,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TAIPA</t>
+          <t>Taipa</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1048,35 +1102,40 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>C - Group Stats</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Score: 87</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>95s</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Python3</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>2026-04-21 20:08</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Ryan</t>
         </is>
@@ -1100,7 +1159,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MACAU</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1110,35 +1169,40 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>C - Group Stats</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>92 pts</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>1 min 28 sec</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>2026-04-21 20:16</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Sandy; Tom</t>
         </is>
@@ -1162,7 +1226,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>UNKNOW</t>
+          <t>Unknow</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1172,31 +1236,36 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>B: Text Parser</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
         <is>
           <t>130 sec</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>2026-04-21 20:23</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Una; Victor</t>
         </is>
